--- a/services_forms/005_it_support_request_form--services_forms.xlsx
+++ b/services_forms/005_it_support_request_form--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -684,12 +684,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['dsl',_'cable_modem',_'fiber',_'satellite',_'dialup']</t>
+          <t>dsl</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['DSL', 'Cable Modem', 'Fiber', 'Satellite', 'Dialup']</t>
+          <t>DSL</t>
         </is>
       </c>
     </row>
@@ -734,29 +734,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[none]</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[None]</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>internet_connection_choices</t>
+          <t>operating_system_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>windows</t>
+          <t>linux</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Windows</t>
+          <t>Linux</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>linux</t>
+          <t>mac</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Mac</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mac</t>
+          <t>chrome_os</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mac</t>
+          <t>Chrome OS</t>
         </is>
       </c>
     </row>
@@ -819,29 +819,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>chrome_os</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chrome OS</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>operating_system_choices</t>
+          <t>support_status_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -870,27 +870,10 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>support_status_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>resolved</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
